--- a/xlsx/Power/p8.xlsx
+++ b/xlsx/Power/p8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AC05E2-46A2-450F-BFD3-0FBF31612BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA04802-5AD0-4100-AF74-30807915DEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{07C0EA15-AEAD-44CB-81A7-E1B69F3BE056}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{07C0EA15-AEAD-44CB-81A7-E1B69F3BE056}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,16 +404,16 @@
         <v>0.83099999999999996</v>
       </c>
       <c r="C1">
-        <v>0.96499999999999997</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="D1">
-        <v>0.995</v>
+        <v>0.91400000000000003</v>
       </c>
       <c r="E1">
-        <v>0.999</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="F1">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="G1">
         <v>1</v>
@@ -436,16 +436,16 @@
         <v>0.79600000000000004</v>
       </c>
       <c r="C2">
-        <v>0.95299999999999996</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="D2">
-        <v>0.99399999999999999</v>
+        <v>0.89200000000000002</v>
       </c>
       <c r="E2">
-        <v>0.998</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -468,13 +468,13 @@
         <v>0.77300000000000002</v>
       </c>
       <c r="C3">
-        <v>0.93500000000000005</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="D3">
         <v>0.98599999999999999</v>
       </c>
       <c r="E3">
-        <v>0.996</v>
+        <v>0.997</v>
       </c>
       <c r="F3">
         <v>0.999</v>
@@ -494,13 +494,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.36699999999999999</v>
+        <v>0.39400000000000002</v>
       </c>
       <c r="B4">
-        <v>0.71799999999999997</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="C4">
-        <v>0.90500000000000003</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="D4">
         <v>0.97</v>
@@ -564,19 +564,19 @@
         <v>0.623</v>
       </c>
       <c r="C6">
-        <v>0.82399999999999995</v>
+        <v>0.96099999999999997</v>
       </c>
       <c r="D6">
-        <v>0.93100000000000005</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="E6">
-        <v>0.98299999999999998</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="F6">
-        <v>0.99199999999999999</v>
+        <v>0.995</v>
       </c>
       <c r="G6">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -596,19 +596,19 @@
         <v>0.57899999999999996</v>
       </c>
       <c r="C7">
-        <v>0.76</v>
+        <v>0.753</v>
       </c>
       <c r="D7">
-        <v>0.88500000000000001</v>
+        <v>0.88100000000000001</v>
       </c>
       <c r="E7">
-        <v>0.95599999999999996</v>
+        <v>0.95699999999999996</v>
       </c>
       <c r="F7">
-        <v>0.98899999999999999</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="G7">
-        <v>0.99099999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -628,19 +628,19 @@
         <v>0.82499999999999996</v>
       </c>
       <c r="C8">
-        <v>0.94899999999999995</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="D8">
-        <v>0.98499999999999999</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="E8">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="F8">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="G8">
         <v>0.997</v>
-      </c>
-      <c r="F8">
-        <v>0.998</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
       </c>
       <c r="H8">
         <v>0.999</v>
@@ -660,28 +660,28 @@
         <v>0.44800000000000001</v>
       </c>
       <c r="C9">
-        <v>0.24399999999999999</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="D9">
-        <v>0.182</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="E9">
-        <v>0.20499999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="F9">
-        <v>0.27700000000000002</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="G9">
-        <v>0.29499999999999998</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="H9">
-        <v>0.376</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="I9">
-        <v>0.45800000000000002</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="J9">
-        <v>0.56699999999999995</v>
+        <v>0.59499999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p8.xlsx
+++ b/xlsx/Power/p8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA04802-5AD0-4100-AF74-30807915DEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFC048A-19DC-4D84-A675-F43CEC2A95E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{07C0EA15-AEAD-44CB-81A7-E1B69F3BE056}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{07C0EA15-AEAD-44CB-81A7-E1B69F3BE056}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,22 +398,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.41399999999999998</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="B1">
         <v>0.83099999999999996</v>
       </c>
       <c r="C1">
-        <v>0.51100000000000001</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="D1">
-        <v>0.91400000000000003</v>
+        <v>0.995</v>
       </c>
       <c r="E1">
-        <v>0.99099999999999999</v>
+        <v>0.999</v>
       </c>
       <c r="F1">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="G1">
         <v>1</v>
@@ -436,16 +436,16 @@
         <v>0.79600000000000004</v>
       </c>
       <c r="C2">
-        <v>0.49199999999999999</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="D2">
-        <v>0.89200000000000002</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="E2">
-        <v>0.98199999999999998</v>
+        <v>0.998</v>
       </c>
       <c r="F2">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -468,13 +468,13 @@
         <v>0.77300000000000002</v>
       </c>
       <c r="C3">
-        <v>0.94899999999999995</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="D3">
         <v>0.98599999999999999</v>
       </c>
       <c r="E3">
-        <v>0.997</v>
+        <v>0.996</v>
       </c>
       <c r="F3">
         <v>0.999</v>
@@ -494,13 +494,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.39400000000000002</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="B4">
-        <v>0.72599999999999998</v>
+        <v>0.71799999999999997</v>
       </c>
       <c r="C4">
-        <v>0.90600000000000003</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="D4">
         <v>0.97</v>
@@ -564,19 +564,19 @@
         <v>0.623</v>
       </c>
       <c r="C6">
-        <v>0.96099999999999997</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="D6">
-        <v>0.96599999999999997</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="E6">
-        <v>0.99099999999999999</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="F6">
-        <v>0.995</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -596,19 +596,19 @@
         <v>0.57899999999999996</v>
       </c>
       <c r="C7">
-        <v>0.753</v>
+        <v>0.76</v>
       </c>
       <c r="D7">
-        <v>0.88100000000000001</v>
+        <v>0.88500000000000001</v>
       </c>
       <c r="E7">
-        <v>0.95699999999999996</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="F7">
-        <v>0.98799999999999999</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="G7">
-        <v>0.99</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -628,19 +628,19 @@
         <v>0.82499999999999996</v>
       </c>
       <c r="C8">
-        <v>5.6000000000000001E-2</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="D8">
-        <v>0.84399999999999997</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="E8">
-        <v>0.97199999999999998</v>
+        <v>0.997</v>
       </c>
       <c r="F8">
-        <v>0.99399999999999999</v>
+        <v>0.998</v>
       </c>
       <c r="G8">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0.999</v>
@@ -660,28 +660,28 @@
         <v>0.44800000000000001</v>
       </c>
       <c r="C9">
-        <v>0.69099999999999995</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="D9">
-        <v>0.98199999999999998</v>
+        <v>0.182</v>
       </c>
       <c r="E9">
-        <v>0.85</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="F9">
-        <v>0.46899999999999997</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="G9">
-        <v>0.39500000000000002</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="H9">
-        <v>0.45400000000000001</v>
+        <v>0.375</v>
       </c>
       <c r="I9">
-        <v>0.50800000000000001</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="J9">
-        <v>0.59499999999999997</v>
+        <v>0.56699999999999995</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p8.xlsx
+++ b/xlsx/Power/p8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFC048A-19DC-4D84-A675-F43CEC2A95E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A96F47-4295-4044-9B28-13573214E650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{07C0EA15-AEAD-44CB-81A7-E1B69F3BE056}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{07C0EA15-AEAD-44CB-81A7-E1B69F3BE056}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,13 +398,13 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.41499999999999998</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="B1">
-        <v>0.83099999999999996</v>
+        <v>0.83199999999999996</v>
       </c>
       <c r="C1">
-        <v>0.96499999999999997</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="D1">
         <v>0.995</v>
@@ -430,13 +430,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.38500000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="B2">
-        <v>0.79600000000000004</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="C2">
-        <v>0.95299999999999996</v>
+        <v>0.95399999999999996</v>
       </c>
       <c r="D2">
         <v>0.99399999999999999</v>
@@ -462,19 +462,19 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.38900000000000001</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="B3">
-        <v>0.77300000000000002</v>
+        <v>0.77800000000000002</v>
       </c>
       <c r="C3">
-        <v>0.93500000000000005</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="D3">
         <v>0.98599999999999999</v>
       </c>
       <c r="E3">
-        <v>0.996</v>
+        <v>0.997</v>
       </c>
       <c r="F3">
         <v>0.999</v>
@@ -494,10 +494,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.36699999999999999</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="B4">
-        <v>0.71799999999999997</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="C4">
         <v>0.90500000000000003</v>
@@ -526,51 +526,51 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.108</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.52900000000000003</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.86499999999999999</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.92800000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.33200000000000002</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="B6">
-        <v>0.623</v>
+        <v>0.621</v>
       </c>
       <c r="C6">
         <v>0.82399999999999995</v>
       </c>
       <c r="D6">
-        <v>0.93100000000000005</v>
+        <v>0.93</v>
       </c>
       <c r="E6">
-        <v>0.98299999999999998</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="F6">
         <v>0.99199999999999999</v>
@@ -590,22 +590,22 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.30199999999999999</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="B7">
-        <v>0.57899999999999996</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="C7">
         <v>0.76</v>
       </c>
       <c r="D7">
-        <v>0.88500000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="E7">
         <v>0.95599999999999996</v>
       </c>
       <c r="F7">
-        <v>0.98899999999999999</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="G7">
         <v>0.99099999999999999</v>
@@ -625,19 +625,19 @@
         <v>0.28599999999999998</v>
       </c>
       <c r="B8">
-        <v>0.82499999999999996</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="C8">
         <v>0.94899999999999995</v>
       </c>
       <c r="D8">
-        <v>0.98499999999999999</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="E8">
-        <v>0.997</v>
+        <v>0.998</v>
       </c>
       <c r="F8">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -657,31 +657,31 @@
         <v>0.22600000000000001</v>
       </c>
       <c r="B9">
-        <v>0.44800000000000001</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="C9">
         <v>0.24399999999999999</v>
       </c>
       <c r="D9">
-        <v>0.182</v>
+        <v>0.184</v>
       </c>
       <c r="E9">
-        <v>0.20499999999999999</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="F9">
-        <v>0.27700000000000002</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G9">
-        <v>0.29499999999999998</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H9">
-        <v>0.375</v>
+        <v>0.377</v>
       </c>
       <c r="I9">
-        <v>0.45800000000000002</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="J9">
-        <v>0.56699999999999995</v>
+        <v>0.57399999999999995</v>
       </c>
     </row>
   </sheetData>
